--- a/pos_sync/Laporan_Migrasi_SO_DN_Outlet_ke_JURI.xlsx
+++ b/pos_sync/Laporan_Migrasi_SO_DN_Outlet_ke_JURI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rekap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Skipped" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Failed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skipped" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failed" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N198"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -5694,12 +5694,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DN-011026-002</t>
+          <t>SLS-081026-001</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RADJAK HOSPITAL CILEUNGSI BOGOR</t>
+          <t>RS IHC TOELOENGREDJO PARE KEDIRI</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -5724,16 +5724,16 @@
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I98" t="b">
         <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>6807000</v>
+        <v>5362000</v>
       </c>
       <c r="K98" t="n">
-        <v>6807000</v>
+        <v>5362000</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5748,12 +5748,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DN-011026-003</t>
+          <t>SLS-081026-002</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RS GRAHA HUSADA LAMPUNG</t>
+          <t>RS PRIMA MEDIKA PEMALANG</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5784,10 +5784,10 @@
         <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>4034200</v>
+        <v>7800895</v>
       </c>
       <c r="K99" t="n">
-        <v>4034200</v>
+        <v>7800895</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5802,12 +5802,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DN-011026-004</t>
+          <t>SLS-081026-003</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CUST260029</t>
+          <t>RSUD KAJEN PEKALONGAN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -5832,16 +5832,16 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I100" t="b">
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>2178000</v>
+        <v>15198700</v>
       </c>
       <c r="K100" t="n">
-        <v>2178000</v>
+        <v>15198700</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5856,12 +5856,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DN-011026-005</t>
+          <t>SLS-081026-004</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RS MUHAMMADIYAH PALEMBANG</t>
+          <t>RSUD NGUDI WALUYO WILINGI BLLTAR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -5886,16 +5886,16 @@
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I101" t="b">
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>6002480</v>
+        <v>13755880</v>
       </c>
       <c r="K101" t="n">
-        <v>6002480</v>
+        <v>13755880</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5910,12 +5910,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DN-011026-006</t>
+          <t>SLS-081026-005</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CUST260029</t>
+          <t>RSU AISYIYAH PONOROGO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -5940,16 +5940,16 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="I102" t="b">
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>19023640</v>
+        <v>10381620</v>
       </c>
       <c r="K102" t="n">
-        <v>19023640</v>
+        <v>10381620</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5964,12 +5964,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DN-011026-008</t>
+          <t>SLS-081026-006</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CUST260044</t>
+          <t>RSUD TEMANGGUNG</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -5994,16 +5994,16 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I103" t="b">
         <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>330600</v>
+        <v>7526280</v>
       </c>
       <c r="K103" t="n">
-        <v>330600</v>
+        <v>7526280</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -6018,12 +6018,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DN-011026-009</t>
+          <t>SLS-081026-007</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+          <t>RSI MUHAMMADIYAH KENDAL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -6048,16 +6048,16 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I104" t="b">
         <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>19023640</v>
+        <v>20404720</v>
       </c>
       <c r="K104" t="n">
-        <v>19023640</v>
+        <v>20404720</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -6072,12 +6072,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DN-011026-010</t>
+          <t>SLS-081026-008</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+          <t>RSI PKU MUH PEKAJANGAN</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6108,10 +6108,10 @@
         <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>2075434</v>
+        <v>10517740</v>
       </c>
       <c r="K105" t="n">
-        <v>2075434</v>
+        <v>10517740</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -6126,12 +6126,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DN-011026-011</t>
+          <t>SLS-081026-009</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+          <t>RSUD JOMBANG</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6156,16 +6156,16 @@
         <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I106" t="b">
         <v>1</v>
       </c>
       <c r="J106" t="n">
-        <v>819000</v>
+        <v>7951600</v>
       </c>
       <c r="K106" t="n">
-        <v>819000</v>
+        <v>7951600</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -6180,12 +6180,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DN-011026-012</t>
+          <t>SLS-081026-010</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6210,16 +6210,16 @@
         <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I107" t="b">
         <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>330600</v>
+        <v>2598000</v>
       </c>
       <c r="K107" t="n">
-        <v>330600</v>
+        <v>2598000</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6234,12 +6234,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DN-011026-013</t>
+          <t>SLS-081026-011</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CUST260029</t>
+          <t>RS DARMAYU MADIUN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6264,16 +6264,16 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I108" t="b">
         <v>1</v>
       </c>
       <c r="J108" t="n">
-        <v>2075434</v>
+        <v>997880</v>
       </c>
       <c r="K108" t="n">
-        <v>2075434</v>
+        <v>997880</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6288,12 +6288,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DN-011026-014</t>
+          <t>SLS-081026-012</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CUST260029</t>
+          <t>RSU MUSLIMAT PONOROGO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6342,12 +6342,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DN-011026-015</t>
+          <t>SLS-081026-013</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RSUD DR HARJONO PONOROGO</t>
+          <t>RSU MUSLIMAT PONOROGO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6372,16 +6372,16 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I110" t="b">
         <v>1</v>
       </c>
       <c r="J110" t="n">
-        <v>12447680</v>
+        <v>2027584</v>
       </c>
       <c r="K110" t="n">
-        <v>12447680</v>
+        <v>2027584</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6396,12 +6396,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DN-011026-016</t>
+          <t>SLS-081026-014</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>RS H.A ZAKY DJUNAID</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6426,16 +6426,16 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I111" t="b">
         <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>4464400</v>
+        <v>5578000</v>
       </c>
       <c r="K111" t="n">
-        <v>4464400</v>
+        <v>5578000</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6450,12 +6450,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DN-011026-017</t>
+          <t>SLS-081026-015</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6465,12 +6465,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>RS PKU WONOSOBO</t>
+          <t>RSU MUSLIMAT PONOROGO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6480,16 +6480,16 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I112" t="b">
         <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>18417580</v>
+        <v>18700640</v>
       </c>
       <c r="K112" t="n">
-        <v>18417580</v>
+        <v>18700640</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6504,12 +6504,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DN-011026-018</t>
+          <t>SLS-081026-016</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>RS PKU WONOSOBO</t>
+          <t>RS PKU MUHAMMADIYAH TEMANGGUNG</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6534,16 +6534,16 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I113" t="b">
         <v>1</v>
       </c>
       <c r="J113" t="n">
-        <v>520000</v>
+        <v>13800620</v>
       </c>
       <c r="K113" t="n">
-        <v>520000</v>
+        <v>13800620</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6558,12 +6558,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DN-011026-019</t>
+          <t>SLS-081026-017</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RSI SITI AISYIYAH MADIUN</t>
+          <t>RS MARZOEKI MAHDI BOGOR</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6588,16 +6588,16 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I114" t="b">
         <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>10049620</v>
+        <v>6182280</v>
       </c>
       <c r="K114" t="n">
-        <v>10049620</v>
+        <v>6182280</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6612,12 +6612,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DN-011026-020</t>
+          <t>SLS-081026-020</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>RS IHC TOELOENGREDJO PARE KEDIRI</t>
+          <t>RS MUHAMMADIYAH PALEMBANG</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6642,16 +6642,16 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I115" t="b">
         <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>3766900</v>
+        <v>1502800</v>
       </c>
       <c r="K115" t="n">
-        <v>3766900</v>
+        <v>1502800</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6666,12 +6666,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DN-011026-022</t>
+          <t>SLS-081026-021</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>RSUD LIMPUNG BATANG</t>
+          <t>RSAI BANDUNG</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6696,16 +6696,16 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I116" t="b">
         <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>9025380</v>
+        <v>570000</v>
       </c>
       <c r="K116" t="n">
-        <v>9025380</v>
+        <v>570000</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6720,12 +6720,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DN-011026-023</t>
+          <t>SLS-081026-022</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>RSUD BATANG</t>
+          <t>RS AMC BANDUNG</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -6750,16 +6750,16 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I117" t="b">
         <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>10717780</v>
+        <v>228000</v>
       </c>
       <c r="K117" t="n">
-        <v>10717780</v>
+        <v>228000</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6774,12 +6774,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DN-011026-024</t>
+          <t>SLS-081026-023</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>RSI PKU MUH PEKAJANGAN</t>
+          <t>RS UNIMEDIKA SETU BEKASI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6804,16 +6804,16 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I118" t="b">
         <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>10356620</v>
+        <v>502500</v>
       </c>
       <c r="K118" t="n">
-        <v>10356620</v>
+        <v>502500</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6828,12 +6828,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DN-011026-025</t>
+          <t>SLS-081026-024</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RSU AISYIYAH PONOROGO</t>
+          <t>RS ISLAM AR-RASYID PALEMBANG</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6858,16 +6858,16 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I119" t="b">
         <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>7471520</v>
+        <v>4670900</v>
       </c>
       <c r="K119" t="n">
-        <v>7471520</v>
+        <v>4670900</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6882,12 +6882,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DN-011026-026</t>
+          <t>SLS-081026-025</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6897,31 +6897,31 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>RSU AISYIYAH PONOROGO</t>
+          <t>RSUD GRATI KABUPATEN PASURUAN</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I120" t="b">
         <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>7471520</v>
+        <v>1315000</v>
       </c>
       <c r="K120" t="n">
-        <v>7471520</v>
+        <v>1315000</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6936,12 +6936,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DN-011026-027</t>
+          <t>SLS-081026-026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>RSUD JOMBANG</t>
+          <t>RS IHC WONOLANGAN PROBOLINGGO</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6966,16 +6966,16 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I121" t="b">
         <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>8161000</v>
+        <v>723600</v>
       </c>
       <c r="K121" t="n">
-        <v>8161000</v>
+        <v>723600</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DN-011026-028</t>
+          <t>SLS-091026-001</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RSUD TEMANGGUNG</t>
+          <t>RSUD DR MOHAMMAD ZYN SAMPANG</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7020,16 +7020,16 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I122" t="b">
         <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>9556800</v>
+        <v>10320480</v>
       </c>
       <c r="K122" t="n">
-        <v>9556800</v>
+        <v>10320480</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -7044,12 +7044,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DN-011026-029</t>
+          <t>SLS-091026-002</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>RSUD SETJONEGORO WONOSOBO</t>
+          <t>RS ISLAM SURABAYA A. YANI</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -7074,16 +7074,16 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
       </c>
       <c r="J123" t="n">
-        <v>16443020</v>
+        <v>6192600</v>
       </c>
       <c r="K123" t="n">
-        <v>16443020</v>
+        <v>6192600</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DN-011026-030</t>
+          <t>DN-011026-002</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>RS PKU MUHAMMADIYAH TEMANGGUNG</t>
+          <t>RADJAK HOSPITAL CILEUNGSI BOGOR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7128,16 +7128,16 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I124" t="b">
         <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>11820600</v>
+        <v>6807000</v>
       </c>
       <c r="K124" t="n">
-        <v>11820600</v>
+        <v>6807000</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DN-011026-031</t>
+          <t>DN-011026-003</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>RSI MUHAMMADIYAH KENDAL</t>
+          <t>RS GRAHA HUSADA LAMPUNG</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7182,16 +7182,16 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I125" t="b">
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>9007000</v>
+        <v>4034200</v>
       </c>
       <c r="K125" t="n">
-        <v>9007000</v>
+        <v>4034200</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DN-011026-032</t>
+          <t>DN-011026-004</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+          <t>CUST260029</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DN-011026-033</t>
+          <t>DN-011026-005</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>RS DARMAYU MADIUN</t>
+          <t>RS MUHAMMADIYAH PALEMBANG</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7290,16 +7290,16 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I127" t="b">
         <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>12942520</v>
+        <v>6002480</v>
       </c>
       <c r="K127" t="n">
-        <v>12942520</v>
+        <v>6002480</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DN-011026-034</t>
+          <t>DN-011026-006</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+          <t>CUST260029</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7344,16 +7344,16 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="I128" t="b">
         <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>420000</v>
+        <v>19023640</v>
       </c>
       <c r="K128" t="n">
-        <v>420000</v>
+        <v>19023640</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DN-011026-035</t>
+          <t>DN-011026-008</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>RS UI DEPOK</t>
+          <t>CUST260044</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7398,16 +7398,16 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I129" t="b">
         <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>12542400</v>
+        <v>330600</v>
       </c>
       <c r="K129" t="n">
-        <v>12542400</v>
+        <v>330600</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DN-021026-001</t>
+          <t>DN-011026-009</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>RS DUTA INDAH JAKARTA</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7452,16 +7452,16 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="I130" t="b">
         <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>9764360</v>
+        <v>19023640</v>
       </c>
       <c r="K130" t="n">
-        <v>9764360</v>
+        <v>19023640</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DN-021026-002</t>
+          <t>DN-011026-010</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>RSI MUHAMMADIYAH KENDAL</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7506,16 +7506,16 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I131" t="b">
         <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>10368000</v>
+        <v>2075434</v>
       </c>
       <c r="K131" t="n">
-        <v>10368000</v>
+        <v>2075434</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DN-021026-003</t>
+          <t>DN-011026-011</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RS ASSAKINAH MEDIKA SIDOARJO</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7560,16 +7560,16 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I132" t="b">
         <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>8308660</v>
+        <v>819000</v>
       </c>
       <c r="K132" t="n">
-        <v>8308660</v>
+        <v>819000</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DN-021026-004</t>
+          <t>DN-011026-012</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RS IHC DJATIROTO LUMAJANG</t>
+          <t>RSU MUSLIMAT PONOROGO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7614,16 +7614,16 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I133" t="b">
         <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>18564700</v>
+        <v>330600</v>
       </c>
       <c r="K133" t="n">
-        <v>18564700</v>
+        <v>330600</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DN-021026-005</t>
+          <t>DN-011026-013</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>RS MUHAMMADIYAH LAMONGAN</t>
+          <t>CUST260029</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7668,16 +7668,16 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I134" t="b">
         <v>1</v>
       </c>
       <c r="J134" t="n">
-        <v>18854140</v>
+        <v>2075434</v>
       </c>
       <c r="K134" t="n">
-        <v>18854140</v>
+        <v>2075434</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DN-021026-006</t>
+          <t>DN-011026-014</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RS MUHAMMADIYAH LAMONGAN</t>
+          <t>CUST260029</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -7722,16 +7722,16 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I135" t="b">
         <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>2075434</v>
+        <v>819000</v>
       </c>
       <c r="K135" t="n">
-        <v>2075434</v>
+        <v>819000</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DN-021026-007</t>
+          <t>DN-011026-015</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RS MUHAMMADIYAH LAMONGAN</t>
+          <t>RSUD DR HARJONO PONOROGO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7776,16 +7776,16 @@
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I136" t="b">
         <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>2476000</v>
+        <v>12447680</v>
       </c>
       <c r="K136" t="n">
-        <v>2476000</v>
+        <v>12447680</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DN-021026-008</t>
+          <t>DN-011026-016</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>RS MUHAMMADIYAH LAMONGAN</t>
+          <t>RS H.A ZAKY DJUNAID</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7830,16 +7830,16 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I137" t="b">
         <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>819000</v>
+        <v>4464400</v>
       </c>
       <c r="K137" t="n">
-        <v>819000</v>
+        <v>4464400</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DN-021026-009</t>
+          <t>DN-011026-017</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RSUD BANGIL KABUPATEN PASURUAN</t>
+          <t>RS PKU WONOSOBO</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7884,16 +7884,16 @@
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I138" t="b">
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>22183000</v>
+        <v>18417580</v>
       </c>
       <c r="K138" t="n">
-        <v>22183000</v>
+        <v>18417580</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DN-021026-010</t>
+          <t>DN-011026-018</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7923,31 +7923,31 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>RS NU TUBAN</t>
+          <t>RS PKU WONOSOBO</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I139" t="b">
         <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>32945900</v>
+        <v>520000</v>
       </c>
       <c r="K139" t="n">
-        <v>32945900</v>
+        <v>520000</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DN-021026-011</t>
+          <t>DN-011026-019</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RSUD DR. HARYOTO LUMAJANG</t>
+          <t>RSI SITI AISYIYAH MADIUN</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7992,16 +7992,16 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I140" t="b">
         <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>14268000</v>
+        <v>10049620</v>
       </c>
       <c r="K140" t="n">
-        <v>14268000</v>
+        <v>10049620</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DN-021026-013</t>
+          <t>DN-011026-020</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>RSI AYSHA CIBINONG BOGOR</t>
+          <t>RS IHC TOELOENGREDJO PARE KEDIRI</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -8046,16 +8046,16 @@
         <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I141" t="b">
         <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>1572400</v>
+        <v>3766900</v>
       </c>
       <c r="K141" t="n">
-        <v>1572400</v>
+        <v>3766900</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DN-021026-014</t>
+          <t>DN-011026-022</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RS ANNISA TANGERANG</t>
+          <t>RSUD LIMPUNG BATANG</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -8100,16 +8100,16 @@
         <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I142" t="b">
         <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>1669200</v>
+        <v>9025380</v>
       </c>
       <c r="K142" t="n">
-        <v>1669200</v>
+        <v>9025380</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DN-051026-001</t>
+          <t>DN-011026-023</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RS RESTU KASIH JAKARTA</t>
+          <t>RSUD BATANG</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -8154,16 +8154,16 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I143" t="b">
         <v>1</v>
       </c>
       <c r="J143" t="n">
-        <v>13872118</v>
+        <v>10717780</v>
       </c>
       <c r="K143" t="n">
-        <v>13872118</v>
+        <v>10717780</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DN-051026-002</t>
+          <t>DN-011026-024</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RS NU TUBAN</t>
+          <t>RSI PKU MUH PEKAJANGAN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -8208,16 +8208,16 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I144" t="b">
         <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>32744900</v>
+        <v>10356620</v>
       </c>
       <c r="K144" t="n">
-        <v>32744900</v>
+        <v>10356620</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DN-051026-003</t>
+          <t>DN-011026-025</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>RSUD TIDAR KOTA MAGELANG</t>
+          <t>RSU AISYIYAH PONOROGO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8262,16 +8262,16 @@
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I145" t="b">
         <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>15357160</v>
+        <v>7471520</v>
       </c>
       <c r="K145" t="n">
-        <v>15357160</v>
+        <v>7471520</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DN-051026-004</t>
+          <t>DN-011026-026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8301,31 +8301,31 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>RS PKU MUHAMMADIYAH GAMPING</t>
+          <t>RSU AISYIYAH PONOROGO</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I146" t="b">
         <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>16378000</v>
+        <v>7471520</v>
       </c>
       <c r="K146" t="n">
-        <v>16378000</v>
+        <v>7471520</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DN-051026-005</t>
+          <t>DN-011026-027</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>RS PKU MUHAMMADIYAH GAMPING</t>
+          <t>RSUD JOMBANG</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8370,16 +8370,16 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I147" t="b">
         <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>3224000</v>
+        <v>8161000</v>
       </c>
       <c r="K147" t="n">
-        <v>3224000</v>
+        <v>8161000</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DN-051026-006</t>
+          <t>DN-011026-028</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8409,12 +8409,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RSUD RAA TJOKRONEGORO</t>
+          <t>RSUD TEMANGGUNG</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -8424,16 +8424,16 @@
         <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I148" t="b">
         <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>8228020</v>
+        <v>9556800</v>
       </c>
       <c r="K148" t="n">
-        <v>8228020</v>
+        <v>9556800</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DN-051026-007</t>
+          <t>DN-011026-029</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>RSUD NYI AGENG SERANG KULON PROGO</t>
+          <t>RSUD SETJONEGORO WONOSOBO</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -8478,16 +8478,16 @@
         <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I149" t="b">
         <v>1</v>
       </c>
       <c r="J149" t="n">
-        <v>5898120</v>
+        <v>16443020</v>
       </c>
       <c r="K149" t="n">
-        <v>5898120</v>
+        <v>16443020</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DN-051026-009</t>
+          <t>DN-011026-030</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RSUD BAGAS WARAS KLATEN</t>
+          <t>RS PKU MUHAMMADIYAH TEMANGGUNG</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8532,16 +8532,16 @@
         <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I150" t="b">
         <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>3511000</v>
+        <v>11820600</v>
       </c>
       <c r="K150" t="n">
-        <v>3511000</v>
+        <v>11820600</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DN-051026-010</t>
+          <t>DN-011026-031</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>RSU AISYIYAH KLATEN</t>
+          <t>RSI MUHAMMADIYAH KENDAL</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8586,16 +8586,16 @@
         <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I151" t="b">
         <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>2426000</v>
+        <v>9007000</v>
       </c>
       <c r="K151" t="n">
-        <v>2426000</v>
+        <v>9007000</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DN-051026-011</t>
+          <t>DN-011026-032</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>RSU QUEEN LATIFA YOGYAKARTA</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8640,16 +8640,16 @@
         <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I152" t="b">
         <v>1</v>
       </c>
       <c r="J152" t="n">
-        <v>8231320</v>
+        <v>2178000</v>
       </c>
       <c r="K152" t="n">
-        <v>8231320</v>
+        <v>2178000</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DN-051026-012</t>
+          <t>DN-011026-033</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>RSUD SLEMAN</t>
+          <t>RS DARMAYU MADIUN</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8694,16 +8694,16 @@
         <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I153" t="b">
         <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>8170180</v>
+        <v>12942520</v>
       </c>
       <c r="K153" t="n">
-        <v>8170180</v>
+        <v>12942520</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DN-051026-013</t>
+          <t>DN-011026-034</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>RSU PUSAT SURAKARTA</t>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -8748,16 +8748,16 @@
         <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I154" t="b">
         <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>8543500</v>
+        <v>420000</v>
       </c>
       <c r="K154" t="n">
-        <v>8543500</v>
+        <v>420000</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DN-051026-014</t>
+          <t>DN-011026-035</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>RS AISYIYAH SITI FATIMAH SIDOARJO</t>
+          <t>RS UI DEPOK</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8802,16 +8802,16 @@
         <v>1</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I155" t="b">
         <v>1</v>
       </c>
       <c r="J155" t="n">
-        <v>534000</v>
+        <v>12542400</v>
       </c>
       <c r="K155" t="n">
-        <v>534000</v>
+        <v>12542400</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DN-051026-018</t>
+          <t>DN-021026-001</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RSI AYSHA CIBINONG BOGOR</t>
+          <t>RS DUTA INDAH JAKARTA</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8856,16 +8856,16 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I156" t="b">
         <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>640000</v>
+        <v>9764360</v>
       </c>
       <c r="K156" t="n">
-        <v>640000</v>
+        <v>9764360</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DN-061026-003</t>
+          <t>DN-021026-002</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8895,31 +8895,31 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>RSUD DR. M. YUNUS BENGKULU</t>
+          <t>RSI MUHAMMADIYAH KENDAL</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I157" t="b">
         <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>10940000</v>
+        <v>10368000</v>
       </c>
       <c r="K157" t="n">
-        <v>10940000</v>
+        <v>10368000</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DN-061026-004</t>
+          <t>DN-021026-003</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>RSUD SEKAYU BANYUASIN</t>
+          <t>RS ASSAKINAH MEDIKA SIDOARJO</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -8964,16 +8964,16 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I158" t="b">
         <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>29486700</v>
+        <v>8308660</v>
       </c>
       <c r="K158" t="n">
-        <v>29486700</v>
+        <v>8308660</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DN-061026-005</t>
+          <t>DN-021026-004</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>RS YOS SUDARSO PADANG</t>
+          <t>RS IHC DJATIROTO LUMAJANG</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -9018,16 +9018,16 @@
         <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I159" t="b">
         <v>1</v>
       </c>
       <c r="J159" t="n">
-        <v>16442440</v>
+        <v>18564700</v>
       </c>
       <c r="K159" t="n">
-        <v>16442440</v>
+        <v>18564700</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DN-061026-006</t>
+          <t>DN-021026-005</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>RUMAH SAKIT UNIVERSITAS ANDALAS PADANG</t>
+          <t>RS MUHAMMADIYAH LAMONGAN</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -9072,16 +9072,16 @@
         <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="I160" t="b">
         <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>3073720</v>
+        <v>18854140</v>
       </c>
       <c r="K160" t="n">
-        <v>3073720</v>
+        <v>18854140</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DN-061026-007</t>
+          <t>DN-021026-006</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9111,12 +9111,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>RSI JAKARTA PONDOK KOPI</t>
+          <t>RS MUHAMMADIYAH LAMONGAN</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -9126,16 +9126,16 @@
         <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I161" t="b">
         <v>1</v>
       </c>
       <c r="J161" t="n">
-        <v>5046440</v>
+        <v>2075434</v>
       </c>
       <c r="K161" t="n">
-        <v>5046440</v>
+        <v>2075434</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DN-061026-009</t>
+          <t>DN-021026-007</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>RSUD DR. M. YUNUS BENGKULU</t>
+          <t>RS MUHAMMADIYAH LAMONGAN</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -9180,16 +9180,16 @@
         <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I162" t="b">
         <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>9140000</v>
+        <v>2476000</v>
       </c>
       <c r="K162" t="n">
-        <v>9140000</v>
+        <v>2476000</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DN-061026-010</t>
+          <t>DN-021026-008</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>RSUD Hj. ANNA LASMANAH BANJARNEGARA</t>
+          <t>RS MUHAMMADIYAH LAMONGAN</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -9234,16 +9234,16 @@
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I163" t="b">
         <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>6257740</v>
+        <v>819000</v>
       </c>
       <c r="K163" t="n">
-        <v>6257740</v>
+        <v>819000</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DN-061026-011</t>
+          <t>DN-021026-009</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LAKSANA BARU SWALAYAN MAJENANG</t>
+          <t>RSUD BANGIL KABUPATEN PASURUAN</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -9288,16 +9288,16 @@
         <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I164" t="b">
         <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>8860420</v>
+        <v>22183000</v>
       </c>
       <c r="K164" t="n">
-        <v>8860420</v>
+        <v>22183000</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DN-061026-012</t>
+          <t>DN-021026-010</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9327,31 +9327,31 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>CUST260016</t>
+          <t>RS NU TUBAN</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I165" t="b">
         <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>10479420</v>
+        <v>32945900</v>
       </c>
       <c r="K165" t="n">
-        <v>10479420</v>
+        <v>32945900</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DN-061026-013</t>
+          <t>DN-021026-011</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>TOSERBA JADI BARU KEBUMEN</t>
+          <t>RSUD DR. HARYOTO LUMAJANG</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -9396,16 +9396,16 @@
         <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I166" t="b">
         <v>1</v>
       </c>
       <c r="J166" t="n">
-        <v>16477300</v>
+        <v>14268000</v>
       </c>
       <c r="K166" t="n">
-        <v>16477300</v>
+        <v>14268000</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DN-061026-014</t>
+          <t>DN-021026-013</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>RSUD AJIBARANG BANYUMAS</t>
+          <t>RSI AYSHA CIBINONG BOGOR</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -9450,16 +9450,16 @@
         <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I167" t="b">
         <v>1</v>
       </c>
       <c r="J167" t="n">
-        <v>11029300</v>
+        <v>1572400</v>
       </c>
       <c r="K167" t="n">
-        <v>11029300</v>
+        <v>1572400</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DN-061026-015</t>
+          <t>DN-021026-014</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9489,12 +9489,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>RSUD BALI MANDARA</t>
+          <t>RS ANNISA TANGERANG</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -9504,16 +9504,16 @@
         <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I168" t="b">
         <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>14065220</v>
+        <v>1669200</v>
       </c>
       <c r="K168" t="n">
-        <v>14065220</v>
+        <v>1669200</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DN-061026-016</t>
+          <t>DN-051026-001</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>RS PRIMA MEDIKA BALI</t>
+          <t>RS RESTU KASIH JAKARTA</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -9558,16 +9558,16 @@
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I169" t="b">
         <v>1</v>
       </c>
       <c r="J169" t="n">
-        <v>9953140</v>
+        <v>13872118</v>
       </c>
       <c r="K169" t="n">
-        <v>9953140</v>
+        <v>13872118</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DN-061026-017</t>
+          <t>DN-051026-002</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RS PKU MUHAMMADIYAH SURABAYA</t>
+          <t>RS NU TUBAN</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -9612,16 +9612,16 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I170" t="b">
         <v>1</v>
       </c>
       <c r="J170" t="n">
-        <v>1198400</v>
+        <v>32744900</v>
       </c>
       <c r="K170" t="n">
-        <v>1198400</v>
+        <v>32744900</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DN-061026-018</t>
+          <t>DN-051026-003</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>TOSERBA JADI BARU BUMIAYU</t>
+          <t>RSUD TIDAR KOTA MAGELANG</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -9666,16 +9666,16 @@
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I171" t="b">
         <v>1</v>
       </c>
       <c r="J171" t="n">
-        <v>5990300</v>
+        <v>15357160</v>
       </c>
       <c r="K171" t="n">
-        <v>5990300</v>
+        <v>15357160</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DN-061026-019</t>
+          <t>DN-051026-004</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RSUD M. NATSIR KOTA SOLOK</t>
+          <t>RS PKU MUHAMMADIYAH GAMPING</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -9720,16 +9720,16 @@
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I172" t="b">
         <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>2598000</v>
+        <v>16378000</v>
       </c>
       <c r="K172" t="n">
-        <v>2598000</v>
+        <v>16378000</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DN-061026-020</t>
+          <t>DN-051026-005</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>RSUD M. NATSIR KOTA SOLOK</t>
+          <t>RS PKU MUHAMMADIYAH GAMPING</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -9774,16 +9774,16 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="I173" t="b">
         <v>1</v>
       </c>
       <c r="J173" t="n">
-        <v>21256540</v>
+        <v>3224000</v>
       </c>
       <c r="K173" t="n">
-        <v>21256540</v>
+        <v>3224000</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DN-061026-021</t>
+          <t>DN-051026-006</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CUST260044</t>
+          <t>RSUD RAA TJOKRONEGORO</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -9828,16 +9828,16 @@
         <v>1</v>
       </c>
       <c r="H174" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I174" t="b">
         <v>1</v>
       </c>
       <c r="J174" t="n">
-        <v>2508000</v>
+        <v>8228020</v>
       </c>
       <c r="K174" t="n">
-        <v>2508000</v>
+        <v>8228020</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DN-061026-022</t>
+          <t>DN-051026-007</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>CUST260044</t>
+          <t>RSUD NYI AGENG SERANG KULON PROGO</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -9882,16 +9882,16 @@
         <v>1</v>
       </c>
       <c r="H175" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I175" t="b">
         <v>1</v>
       </c>
       <c r="J175" t="n">
-        <v>2076434</v>
+        <v>5898120</v>
       </c>
       <c r="K175" t="n">
-        <v>2076434</v>
+        <v>5898120</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DN-061026-023</t>
+          <t>DN-051026-009</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>CUST260044</t>
+          <t>RSUD BAGAS WARAS KLATEN</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -9936,16 +9936,16 @@
         <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I176" t="b">
         <v>1</v>
       </c>
       <c r="J176" t="n">
-        <v>819000</v>
+        <v>3511000</v>
       </c>
       <c r="K176" t="n">
-        <v>819000</v>
+        <v>3511000</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DN-061026-024</t>
+          <t>DN-051026-010</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RSUD SEKAYU BANYUASIN</t>
+          <t>RSU AISYIYAH KLATEN</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -9990,16 +9990,16 @@
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I177" t="b">
         <v>1</v>
       </c>
       <c r="J177" t="n">
-        <v>270000</v>
+        <v>2426000</v>
       </c>
       <c r="K177" t="n">
-        <v>270000</v>
+        <v>2426000</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DN-061026-025</t>
+          <t>DN-051026-011</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>CUST260044</t>
+          <t>RSU QUEEN LATIFA YOGYAKARTA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -10044,16 +10044,16 @@
         <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I178" t="b">
         <v>1</v>
       </c>
       <c r="J178" t="n">
-        <v>23078540</v>
+        <v>8231320</v>
       </c>
       <c r="K178" t="n">
-        <v>23078540</v>
+        <v>8231320</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DN-061026-026</t>
+          <t>DN-051026-012</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RSUD M. NATSIR KOTA SOLOK</t>
+          <t>RSUD SLEMAN</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -10098,16 +10098,16 @@
         <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I179" t="b">
         <v>1</v>
       </c>
       <c r="J179" t="n">
-        <v>819000</v>
+        <v>8170180</v>
       </c>
       <c r="K179" t="n">
-        <v>819000</v>
+        <v>8170180</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DN-061026-027</t>
+          <t>DN-051026-013</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>RSUD M. NATSIR KOTA SOLOK</t>
+          <t>RSU PUSAT SURAKARTA</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -10152,16 +10152,16 @@
         <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I180" t="b">
         <v>1</v>
       </c>
       <c r="J180" t="n">
-        <v>2760434</v>
+        <v>8543500</v>
       </c>
       <c r="K180" t="n">
-        <v>2760434</v>
+        <v>8543500</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DN-061026-028</t>
+          <t>DN-051026-014</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>RSUD NYI AGENG SERANG KULON PROGO</t>
+          <t>RS AISYIYAH SITI FATIMAH SIDOARJO</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -10212,10 +10212,10 @@
         <v>1</v>
       </c>
       <c r="J181" t="n">
-        <v>186000</v>
+        <v>534000</v>
       </c>
       <c r="K181" t="n">
-        <v>186000</v>
+        <v>534000</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DN-061026-029</t>
+          <t>DN-051026-018</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>RSU QUEEN LATIFA YOGYAKARTA</t>
+          <t>RSI AYSHA CIBINONG BOGOR</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -10260,16 +10260,16 @@
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I182" t="b">
         <v>1</v>
       </c>
       <c r="J182" t="n">
-        <v>155000</v>
+        <v>640000</v>
       </c>
       <c r="K182" t="n">
-        <v>155000</v>
+        <v>640000</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DN-061026-030</t>
+          <t>DN-061026-003</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>RSUD SLEMAN</t>
+          <t>RSUD DR. M. YUNUS BENGKULU</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10308,22 +10308,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I183" t="b">
         <v>1</v>
       </c>
       <c r="J183" t="n">
-        <v>155000</v>
+        <v>10940000</v>
       </c>
       <c r="K183" t="n">
-        <v>155000</v>
+        <v>10940000</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DN-061026-031</t>
+          <t>DN-061026-004</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>RSU PUSAT SURAKARTA</t>
+          <t>RSUD SEKAYU BANYUASIN</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10368,16 +10368,16 @@
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I184" t="b">
         <v>1</v>
       </c>
       <c r="J184" t="n">
-        <v>93000</v>
+        <v>29486700</v>
       </c>
       <c r="K184" t="n">
-        <v>93000</v>
+        <v>29486700</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DN-061026-033</t>
+          <t>DN-061026-005</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>RS NU TUBAN</t>
+          <t>RS YOS SUDARSO PADANG</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10422,16 +10422,16 @@
         <v>1</v>
       </c>
       <c r="H185" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I185" t="b">
         <v>1</v>
       </c>
       <c r="J185" t="n">
-        <v>201000</v>
+        <v>16442440</v>
       </c>
       <c r="K185" t="n">
-        <v>201000</v>
+        <v>16442440</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DN-071026-001</t>
+          <t>DN-061026-006</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>RSUD DR GONDO SUWARNO UNGARAN</t>
+          <t>RUMAH SAKIT UNIVERSITAS ANDALAS PADANG</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -10476,16 +10476,16 @@
         <v>1</v>
       </c>
       <c r="H186" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I186" t="b">
         <v>1</v>
       </c>
       <c r="J186" t="n">
-        <v>15737900</v>
+        <v>3073720</v>
       </c>
       <c r="K186" t="n">
-        <v>15737900</v>
+        <v>3073720</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DN-071026-002</t>
+          <t>DN-061026-007</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>RS IHC WONOLANGAN PROBOLINGGO</t>
+          <t>RSI JAKARTA PONDOK KOPI</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -10530,16 +10530,16 @@
         <v>1</v>
       </c>
       <c r="H187" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I187" t="b">
         <v>1</v>
       </c>
       <c r="J187" t="n">
-        <v>841000</v>
+        <v>5046440</v>
       </c>
       <c r="K187" t="n">
-        <v>841000</v>
+        <v>5046440</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DN-071026-003</t>
+          <t>DN-061026-009</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10569,12 +10569,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>RSUD DR. MOCH. ANSARI SALEH KALSEL</t>
+          <t>RSUD DR. M. YUNUS BENGKULU</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -10590,10 +10590,10 @@
         <v>1</v>
       </c>
       <c r="J188" t="n">
-        <v>1635500</v>
+        <v>9140000</v>
       </c>
       <c r="K188" t="n">
-        <v>1635500</v>
+        <v>9140000</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DN-071026-004</t>
+          <t>DN-061026-010</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>RS SARKIES AISYIYAH KUDUS</t>
+          <t>RSUD Hj. ANNA LASMANAH BANJARNEGARA</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I189" t="b">
         <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>6913940</v>
+        <v>6257740</v>
       </c>
       <c r="K189" t="n">
-        <v>6913940</v>
+        <v>6257740</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DN-071026-005</t>
+          <t>DN-061026-011</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>RS NASIONAL DIPONEGORO SEMARANG</t>
+          <t>LAKSANA BARU SWALAYAN MAJENANG</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -10692,16 +10692,16 @@
         <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I190" t="b">
         <v>1</v>
       </c>
       <c r="J190" t="n">
-        <v>10868100</v>
+        <v>8860420</v>
       </c>
       <c r="K190" t="n">
-        <v>10868100</v>
+        <v>8860420</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DN-071026-006</t>
+          <t>DN-061026-012</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>RSUD DR. R. SOETIJONO BLORA</t>
+          <t>CUST260016</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -10746,16 +10746,16 @@
         <v>1</v>
       </c>
       <c r="H191" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I191" t="b">
         <v>1</v>
       </c>
       <c r="J191" t="n">
-        <v>8053860</v>
+        <v>10479420</v>
       </c>
       <c r="K191" t="n">
-        <v>8053860</v>
+        <v>10479420</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DN-071026-007</t>
+          <t>DN-061026-013</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10785,12 +10785,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>RSUD R.A KARTINI JEPARA</t>
+          <t>TOSERBA JADI BARU KEBUMEN</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -10800,16 +10800,16 @@
         <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I192" t="b">
         <v>1</v>
       </c>
       <c r="J192" t="n">
-        <v>8638364</v>
+        <v>16477300</v>
       </c>
       <c r="K192" t="n">
-        <v>8638364</v>
+        <v>16477300</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DN-071026-008</t>
+          <t>DN-061026-014</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>RSUD SULTAN FATAH DEMAK</t>
+          <t>RSUD AJIBARANG BANYUMAS</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -10854,16 +10854,16 @@
         <v>1</v>
       </c>
       <c r="H193" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I193" t="b">
         <v>1</v>
       </c>
       <c r="J193" t="n">
-        <v>1686520</v>
+        <v>11029300</v>
       </c>
       <c r="K193" t="n">
-        <v>1686520</v>
+        <v>11029300</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DN-071026-009</t>
+          <t>DN-061026-015</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>RS ISLAM SAKINAH MOJOKERTO</t>
+          <t>RSUD BALI MANDARA</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -10908,16 +10908,16 @@
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I194" t="b">
         <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1479280</v>
+        <v>14065220</v>
       </c>
       <c r="K194" t="n">
-        <v>1479280</v>
+        <v>14065220</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DN-071026-010</t>
+          <t>DN-061026-016</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>RS DUSTIRA CIMAHI</t>
+          <t>RS PRIMA MEDIKA BALI</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -10962,16 +10962,16 @@
         <v>1</v>
       </c>
       <c r="H195" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I195" t="b">
         <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>12657600</v>
+        <v>9953140</v>
       </c>
       <c r="K195" t="n">
-        <v>12657600</v>
+        <v>9953140</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DN-071026-011</t>
+          <t>DN-061026-017</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>RS AMC BANDUNG</t>
+          <t>RS PKU MUHAMMADIYAH SURABAYA</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -11016,16 +11016,16 @@
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I196" t="b">
         <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>8091840</v>
+        <v>1198400</v>
       </c>
       <c r="K196" t="n">
-        <v>8091840</v>
+        <v>1198400</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DN-071026-012</t>
+          <t>DN-061026-018</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>RSAI BANDUNG</t>
+          <t>TOSERBA JADI BARU BUMIAYU</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -11070,16 +11070,16 @@
         <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I197" t="b">
         <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>17095680</v>
+        <v>5990300</v>
       </c>
       <c r="K197" t="n">
-        <v>17095680</v>
+        <v>5990300</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -11099,51 +11099,2805 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
+          <t>DN-061026-019</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>RSUD M. NATSIR KOTA SOLOK</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="n">
+        <v>21</v>
+      </c>
+      <c r="I198" t="b">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>2598000</v>
+      </c>
+      <c r="K198" t="n">
+        <v>2598000</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M198" t="b">
+        <v>1</v>
+      </c>
+      <c r="N198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>DN-061026-020</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RSUD M. NATSIR KOTA SOLOK</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>37</v>
+      </c>
+      <c r="I199" t="b">
+        <v>1</v>
+      </c>
+      <c r="J199" t="n">
+        <v>21256540</v>
+      </c>
+      <c r="K199" t="n">
+        <v>21256540</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M199" t="b">
+        <v>1</v>
+      </c>
+      <c r="N199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>DN-061026-021</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CUST260044</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>20</v>
+      </c>
+      <c r="I200" t="b">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>2508000</v>
+      </c>
+      <c r="K200" t="n">
+        <v>2508000</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M200" t="b">
+        <v>1</v>
+      </c>
+      <c r="N200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DN-061026-022</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CUST260044</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="n">
+        <v>28</v>
+      </c>
+      <c r="I201" t="b">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>2076434</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2076434</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M201" t="b">
+        <v>1</v>
+      </c>
+      <c r="N201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>DN-061026-023</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CUST260044</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="n">
+        <v>5</v>
+      </c>
+      <c r="I202" t="b">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>819000</v>
+      </c>
+      <c r="K202" t="n">
+        <v>819000</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M202" t="b">
+        <v>1</v>
+      </c>
+      <c r="N202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>DN-061026-024</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>RSUD SEKAYU BANYUASIN</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="b">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>270000</v>
+      </c>
+      <c r="K203" t="n">
+        <v>270000</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M203" t="b">
+        <v>1</v>
+      </c>
+      <c r="N203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>DN-061026-025</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>CUST260044</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>36</v>
+      </c>
+      <c r="I204" t="b">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>23078540</v>
+      </c>
+      <c r="K204" t="n">
+        <v>23078540</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M204" t="b">
+        <v>1</v>
+      </c>
+      <c r="N204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>DN-061026-026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>RSUD M. NATSIR KOTA SOLOK</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="n">
+        <v>5</v>
+      </c>
+      <c r="I205" t="b">
+        <v>1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>819000</v>
+      </c>
+      <c r="K205" t="n">
+        <v>819000</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M205" t="b">
+        <v>1</v>
+      </c>
+      <c r="N205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DN-061026-027</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>RSUD M. NATSIR KOTA SOLOK</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="n">
+        <v>29</v>
+      </c>
+      <c r="I206" t="b">
+        <v>1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>2760434</v>
+      </c>
+      <c r="K206" t="n">
+        <v>2760434</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M206" t="b">
+        <v>1</v>
+      </c>
+      <c r="N206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DN-061026-028</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>RSUD NYI AGENG SERANG KULON PROGO</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" t="b">
+        <v>1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>186000</v>
+      </c>
+      <c r="K207" t="n">
+        <v>186000</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M207" t="b">
+        <v>1</v>
+      </c>
+      <c r="N207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DN-061026-029</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>RSU QUEEN LATIFA YOGYAKARTA</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" t="b">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>155000</v>
+      </c>
+      <c r="K208" t="n">
+        <v>155000</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M208" t="b">
+        <v>1</v>
+      </c>
+      <c r="N208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>DN-061026-030</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>RSUD SLEMAN</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" t="b">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>155000</v>
+      </c>
+      <c r="K209" t="n">
+        <v>155000</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M209" t="b">
+        <v>1</v>
+      </c>
+      <c r="N209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>DN-061026-031</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>RSU PUSAT SURAKARTA</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="b">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>93000</v>
+      </c>
+      <c r="K210" t="n">
+        <v>93000</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M210" t="b">
+        <v>1</v>
+      </c>
+      <c r="N210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DN-061026-033</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RS NU TUBAN</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="b">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>201000</v>
+      </c>
+      <c r="K211" t="n">
+        <v>201000</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M211" t="b">
+        <v>1</v>
+      </c>
+      <c r="N211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>DN-071026-001</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>RSUD DR GONDO SUWARNO UNGARAN</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="n">
+        <v>20</v>
+      </c>
+      <c r="I212" t="b">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>15737900</v>
+      </c>
+      <c r="K212" t="n">
+        <v>15737900</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M212" t="b">
+        <v>1</v>
+      </c>
+      <c r="N212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DN-071026-002</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RS IHC WONOLANGAN PROBOLINGGO</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="n">
+        <v>3</v>
+      </c>
+      <c r="I213" t="b">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>841000</v>
+      </c>
+      <c r="K213" t="n">
+        <v>841000</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M213" t="b">
+        <v>1</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DN-071026-003</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>RSUD DR. MOCH. ANSARI SALEH KALSEL</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>11</v>
+      </c>
+      <c r="I214" t="b">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1635500</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1635500</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M214" t="b">
+        <v>1</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>DN-071026-004</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RS SARKIES AISYIYAH KUDUS</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="n">
+        <v>18</v>
+      </c>
+      <c r="I215" t="b">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>6913940</v>
+      </c>
+      <c r="K215" t="n">
+        <v>6913940</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M215" t="b">
+        <v>1</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DN-071026-005</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>RS NASIONAL DIPONEGORO SEMARANG</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>23</v>
+      </c>
+      <c r="I216" t="b">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>10868100</v>
+      </c>
+      <c r="K216" t="n">
+        <v>10868100</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M216" t="b">
+        <v>1</v>
+      </c>
+      <c r="N216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>DN-071026-006</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>RSUD DR. R. SOETIJONO BLORA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>13</v>
+      </c>
+      <c r="I217" t="b">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>8053860</v>
+      </c>
+      <c r="K217" t="n">
+        <v>8053860</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M217" t="b">
+        <v>1</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>DN-071026-007</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>RSUD R.A KARTINI JEPARA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="n">
+        <v>22</v>
+      </c>
+      <c r="I218" t="b">
+        <v>1</v>
+      </c>
+      <c r="J218" t="n">
+        <v>8638364</v>
+      </c>
+      <c r="K218" t="n">
+        <v>8638364</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M218" t="b">
+        <v>1</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>DN-071026-008</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RSUD SULTAN FATAH DEMAK</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>13</v>
+      </c>
+      <c r="I219" t="b">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1686520</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1686520</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M219" t="b">
+        <v>1</v>
+      </c>
+      <c r="N219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DN-071026-009</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>RS ISLAM SAKINAH MOJOKERTO</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="n">
+        <v>5</v>
+      </c>
+      <c r="I220" t="b">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1479280</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1479280</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M220" t="b">
+        <v>1</v>
+      </c>
+      <c r="N220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DN-071026-010</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>RS DUSTIRA CIMAHI</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>20</v>
+      </c>
+      <c r="I221" t="b">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>12657600</v>
+      </c>
+      <c r="K221" t="n">
+        <v>12657600</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M221" t="b">
+        <v>1</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DN-071026-011</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>RS AMC BANDUNG</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>16</v>
+      </c>
+      <c r="I222" t="b">
+        <v>1</v>
+      </c>
+      <c r="J222" t="n">
+        <v>8091840</v>
+      </c>
+      <c r="K222" t="n">
+        <v>8091840</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M222" t="b">
+        <v>1</v>
+      </c>
+      <c r="N222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DN-071026-012</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>RSAI BANDUNG</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>17</v>
+      </c>
+      <c r="I223" t="b">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>17095680</v>
+      </c>
+      <c r="K223" t="n">
+        <v>17095680</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M223" t="b">
+        <v>1</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
           <t>DN-071026-013</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>PT. JUARA ROTI INDONESIA</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
         <is>
           <t>RS PELABUHAN CIREBON</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="n">
+      <c r="F224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
         <v>11</v>
       </c>
-      <c r="I198" t="b">
-        <v>1</v>
-      </c>
-      <c r="J198" t="n">
+      <c r="I224" t="b">
+        <v>1</v>
+      </c>
+      <c r="J224" t="n">
         <v>6717800</v>
       </c>
-      <c r="K198" t="n">
+      <c r="K224" t="n">
         <v>6717800</v>
       </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>ADA</t>
-        </is>
-      </c>
-      <c r="M198" t="b">
-        <v>1</v>
-      </c>
-      <c r="N198" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M224" t="b">
+        <v>1</v>
+      </c>
+      <c r="N224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>DN-081026-001</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RS IHC TOELOENGREDJO PARE KEDIRI</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>7</v>
+      </c>
+      <c r="I225" t="b">
+        <v>1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>5362000</v>
+      </c>
+      <c r="K225" t="n">
+        <v>5362000</v>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M225" t="b">
+        <v>1</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>DN-081026-002</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>RS PRIMA MEDIKA PEMALANG</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>15</v>
+      </c>
+      <c r="I226" t="b">
+        <v>1</v>
+      </c>
+      <c r="J226" t="n">
+        <v>7800895</v>
+      </c>
+      <c r="K226" t="n">
+        <v>7800895</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M226" t="b">
+        <v>1</v>
+      </c>
+      <c r="N226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DN-081026-003</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>RSUD KAJEN PEKALONGAN</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>18</v>
+      </c>
+      <c r="I227" t="b">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>15198700</v>
+      </c>
+      <c r="K227" t="n">
+        <v>15198700</v>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M227" t="b">
+        <v>1</v>
+      </c>
+      <c r="N227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>DN-081026-004</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>RSUD NGUDI WALUYO WILINGI BLLTAR</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="n">
+        <v>20</v>
+      </c>
+      <c r="I228" t="b">
+        <v>1</v>
+      </c>
+      <c r="J228" t="n">
+        <v>13755880</v>
+      </c>
+      <c r="K228" t="n">
+        <v>13755880</v>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M228" t="b">
+        <v>1</v>
+      </c>
+      <c r="N228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>DN-081026-005</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RSU AISYIYAH PONOROGO</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" t="n">
+        <v>13</v>
+      </c>
+      <c r="I229" t="b">
+        <v>1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>10381620</v>
+      </c>
+      <c r="K229" t="n">
+        <v>10381620</v>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M229" t="b">
+        <v>1</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>DN-081026-006</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RSUD TEMANGGUNG</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>20</v>
+      </c>
+      <c r="I230" t="b">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>7526280</v>
+      </c>
+      <c r="K230" t="n">
+        <v>7526280</v>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M230" t="b">
+        <v>1</v>
+      </c>
+      <c r="N230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>DN-081026-007</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>RSI MUHAMMADIYAH KENDAL</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>16</v>
+      </c>
+      <c r="I231" t="b">
+        <v>1</v>
+      </c>
+      <c r="J231" t="n">
+        <v>20404720</v>
+      </c>
+      <c r="K231" t="n">
+        <v>20404720</v>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M231" t="b">
+        <v>1</v>
+      </c>
+      <c r="N231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DN-081026-008</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>RSI PKU MUH PEKAJANGAN</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="n">
+        <v>28</v>
+      </c>
+      <c r="I232" t="b">
+        <v>1</v>
+      </c>
+      <c r="J232" t="n">
+        <v>10517740</v>
+      </c>
+      <c r="K232" t="n">
+        <v>10517740</v>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M232" t="b">
+        <v>1</v>
+      </c>
+      <c r="N232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>DN-081026-009</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>RSUD JOMBANG</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>26</v>
+      </c>
+      <c r="I233" t="b">
+        <v>1</v>
+      </c>
+      <c r="J233" t="n">
+        <v>7951600</v>
+      </c>
+      <c r="K233" t="n">
+        <v>7951600</v>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M233" t="b">
+        <v>1</v>
+      </c>
+      <c r="N233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>DN-081026-010</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>RSU MUSLIMAT PONOROGO</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>21</v>
+      </c>
+      <c r="I234" t="b">
+        <v>1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>2598000</v>
+      </c>
+      <c r="K234" t="n">
+        <v>2598000</v>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M234" t="b">
+        <v>1</v>
+      </c>
+      <c r="N234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DN-081026-011</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RS DARMAYU MADIUN</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>10</v>
+      </c>
+      <c r="I235" t="b">
+        <v>1</v>
+      </c>
+      <c r="J235" t="n">
+        <v>997880</v>
+      </c>
+      <c r="K235" t="n">
+        <v>997880</v>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M235" t="b">
+        <v>1</v>
+      </c>
+      <c r="N235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DN-081026-012</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>RSU MUSLIMAT PONOROGO</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>5</v>
+      </c>
+      <c r="I236" t="b">
+        <v>1</v>
+      </c>
+      <c r="J236" t="n">
+        <v>819000</v>
+      </c>
+      <c r="K236" t="n">
+        <v>819000</v>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M236" t="b">
+        <v>1</v>
+      </c>
+      <c r="N236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DN-081026-013</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>RSU MUSLIMAT PONOROGO</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>27</v>
+      </c>
+      <c r="I237" t="b">
+        <v>1</v>
+      </c>
+      <c r="J237" t="n">
+        <v>2017584</v>
+      </c>
+      <c r="K237" t="n">
+        <v>2017584</v>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M237" t="b">
+        <v>1</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DN-081026-014</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RS KRISTEN NGESTI WALUYO TEMANGGUNG</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>8</v>
+      </c>
+      <c r="I238" t="b">
+        <v>1</v>
+      </c>
+      <c r="J238" t="n">
+        <v>5578000</v>
+      </c>
+      <c r="K238" t="n">
+        <v>5578000</v>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M238" t="b">
+        <v>1</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DN-081026-015</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RSU MUSLIMAT PONOROGO</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" t="n">
+        <v>36</v>
+      </c>
+      <c r="I239" t="b">
+        <v>1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>18579640</v>
+      </c>
+      <c r="K239" t="n">
+        <v>18579640</v>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M239" t="b">
+        <v>1</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DN-081026-016</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>RS MARZOEKI MAHDI BOGOR</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>22</v>
+      </c>
+      <c r="I240" t="b">
+        <v>1</v>
+      </c>
+      <c r="J240" t="n">
+        <v>6182280</v>
+      </c>
+      <c r="K240" t="n">
+        <v>6182280</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M240" t="b">
+        <v>1</v>
+      </c>
+      <c r="N240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DN-081026-018</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>RS PKU MUHAMMADIYAH TEMANGGUNG</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>25</v>
+      </c>
+      <c r="I241" t="b">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>13800620</v>
+      </c>
+      <c r="K241" t="n">
+        <v>13800620</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M241" t="b">
+        <v>1</v>
+      </c>
+      <c r="N241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>DN-081026-019</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>RS MUHAMMADIYAH PALEMBANG</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>11</v>
+      </c>
+      <c r="I242" t="b">
+        <v>1</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1502800</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1502800</v>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M242" t="b">
+        <v>1</v>
+      </c>
+      <c r="N242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DN-081026-020</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>RSAI BANDUNG</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" t="b">
+        <v>1</v>
+      </c>
+      <c r="J243" t="n">
+        <v>570000</v>
+      </c>
+      <c r="K243" t="n">
+        <v>570000</v>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M243" t="b">
+        <v>1</v>
+      </c>
+      <c r="N243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DN-081026-021</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>RS AMC BANDUNG</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="b">
+        <v>1</v>
+      </c>
+      <c r="J244" t="n">
+        <v>228000</v>
+      </c>
+      <c r="K244" t="n">
+        <v>228000</v>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M244" t="b">
+        <v>1</v>
+      </c>
+      <c r="N244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DN-081026-022</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RS UNIMEDIKA SETU BEKASI</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" t="n">
+        <v>7</v>
+      </c>
+      <c r="I245" t="b">
+        <v>1</v>
+      </c>
+      <c r="J245" t="n">
+        <v>502500</v>
+      </c>
+      <c r="K245" t="n">
+        <v>502500</v>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M245" t="b">
+        <v>1</v>
+      </c>
+      <c r="N245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DN-081026-023</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>RS ISLAM AR-RASYID PALEMBANG</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>1</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" t="n">
+        <v>19</v>
+      </c>
+      <c r="I246" t="b">
+        <v>1</v>
+      </c>
+      <c r="J246" t="n">
+        <v>4624400</v>
+      </c>
+      <c r="K246" t="n">
+        <v>4624400</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M246" t="b">
+        <v>1</v>
+      </c>
+      <c r="N246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DN-081026-024</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>RSUD AJIBARANG BANYUMAS</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
+      </c>
+      <c r="I247" t="b">
+        <v>1</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="K247" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M247" t="b">
+        <v>1</v>
+      </c>
+      <c r="N247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DN-081026-025</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RSUD GRATI KABUPATEN PASURUAN</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" t="n">
+        <v>5</v>
+      </c>
+      <c r="I248" t="b">
+        <v>1</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1315000</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1315000</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M248" t="b">
+        <v>1</v>
+      </c>
+      <c r="N248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DN-081026-026</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>PT. JUARA ROTI INDONESIA</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>RS IHC WONOLANGAN PROBOLINGGO</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" t="b">
+        <v>1</v>
+      </c>
+      <c r="J249" t="n">
+        <v>723600</v>
+      </c>
+      <c r="K249" t="n">
+        <v>723600</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="M249" t="b">
+        <v>1</v>
+      </c>
+      <c r="N249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11156,7 +13910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="3" max="3"/>
@@ -11357,7 +14111,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SLS-300926-012</t>
+          <t>SLS-081026-018</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11369,34 +14123,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DN-011026-007</t>
+          <t>SLS-081026-019</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-300926-012</t>
+          <t>tanpa inter_company_order_reference (bukan intercompany)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Delivery Note</t>
+          <t>Sales Order</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DN-051026-008</t>
+          <t>SLS-300926-012</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delanggu (sudah dimigrasi sesi intercompany)</t>
+          <t>tanpa inter_company_order_reference (bukan intercompany)</t>
         </is>
       </c>
     </row>
@@ -11408,12 +14162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DN-051026-015</t>
+          <t>DN-011026-007</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-014</t>
+          <t>menarik SO di luar scope: SLS-300926-012</t>
         </is>
       </c>
     </row>
@@ -11425,12 +14179,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DN-051026-016</t>
+          <t>DN-051026-008</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-011026-037</t>
+          <t>Delanggu (sudah dimigrasi sesi intercompany)</t>
         </is>
       </c>
     </row>
@@ -11442,12 +14196,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DN-051026-017</t>
+          <t>DN-051026-015</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-011026-037</t>
+          <t>menarik SO di luar scope: SLS-051026-014</t>
         </is>
       </c>
     </row>
@@ -11459,12 +14213,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DN-061026-001</t>
+          <t>DN-051026-016</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-018</t>
+          <t>menarik SO di luar scope: SLS-011026-037</t>
         </is>
       </c>
     </row>
@@ -11476,12 +14230,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DN-061026-002</t>
+          <t>DN-051026-017</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-020</t>
+          <t>menarik SO di luar scope: SLS-011026-037</t>
         </is>
       </c>
     </row>
@@ -11493,12 +14247,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DN-061026-008</t>
+          <t>DN-061026-001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-061026-016</t>
+          <t>menarik SO di luar scope: SLS-051026-018</t>
         </is>
       </c>
     </row>
@@ -11510,12 +14264,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DN-061026-032</t>
+          <t>DN-061026-002</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-014</t>
+          <t>menarik SO di luar scope: SLS-051026-020</t>
         </is>
       </c>
     </row>
@@ -11527,12 +14281,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DN-071026-014</t>
+          <t>DN-061026-008</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-019</t>
+          <t>menarik SO di luar scope: SLS-061026-016</t>
         </is>
       </c>
     </row>
@@ -11544,12 +14298,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DN-071026-015</t>
+          <t>DN-061026-032</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>menarik SO di luar scope: SLS-051026-017</t>
+          <t>menarik SO di luar scope: SLS-051026-014</t>
         </is>
       </c>
     </row>
@@ -11561,12 +14315,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>DN-071026-014</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>menarik SO di luar scope: SLS-051026-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DN-071026-015</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>menarik SO di luar scope: SLS-051026-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>DN-071026-016</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>menarik SO di luar scope: SLS-071026-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DN-081026-017</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>menarik SO di luar scope: SLS-081026-019</t>
         </is>
       </c>
     </row>
@@ -11613,7 +14418,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96/96</t>
+          <t>122/122</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11630,7 +14435,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>789,845,452 vs 789,845,452</t>
+          <t>965,474,771 vs 965,474,771</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11647,7 +14452,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>96/96</t>
+          <t>122/122</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11664,7 +14469,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96/96</t>
+          <t>122/122</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11681,7 +14486,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>96/96</t>
+          <t>122/122</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11698,7 +14503,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>101/101</t>
+          <t>126/126</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11715,7 +14520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>828,760,352 vs 828,760,352</t>
+          <t>988,939,091 vs 988,939,091</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11732,7 +14537,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>101/101</t>
+          <t>126/126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11749,7 +14554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>101/101</t>
+          <t>126/126</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11766,7 +14571,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>101/101</t>
+          <t>126/126</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11783,7 +14588,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
